--- a/data/trans_bre/IP16A07-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP16A07-Provincia-trans_bre.xlsx
@@ -602,7 +602,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -702,7 +702,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,6</t>
+          <t>0,0; 7,05</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -802,7 +802,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -965,7 +965,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,1</t>
+          <t>0,0; 19,9</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1102,7 +1102,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1202,7 +1202,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,9</t>
+          <t>0,0; 10,44</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,77</t>
+          <t>0,0; 36,32</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,21</t>
+          <t>0,0; 2,23</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1475,7 +1475,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,3; 3,48</t>
+          <t>0,31; 3,76</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">

--- a/data/trans_bre/IP16A07-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP16A07-Provincia-trans_bre.xlsx
@@ -775,7 +775,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,05</t>
+          <t>0,0; 6,96</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -965,7 +965,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,9</t>
+          <t>0,0; 16,42</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,44</t>
+          <t>0,0; 11,34</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,32</t>
+          <t>0,0; 40,03</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,23</t>
+          <t>0,0; 2,56</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1475,7 +1475,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,31; 3,76</t>
+          <t>0,28; 3,24</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">

--- a/data/trans_bre/IP16A07-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP16A07-Provincia-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero pastillas para dormir</t>
+          <t>Menores que consumieron pastillas para dormir</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,3</t>
+          <t>2,24</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,96</t>
+          <t>0,0; 11,5</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -965,7 +965,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,42</t>
+          <t>0,0; 14,1</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1,97</t>
+          <t>1,79</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,34</t>
+          <t>0,0; 8,06</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8,79</t>
+          <t>8,56</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,03</t>
+          <t>0,0; 38,49</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1,19</t>
+          <t>1,44</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,56</t>
+          <t>0,0; 2,21</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1475,7 +1475,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,28; 3,24</t>
+          <t>0,37; 4,28</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
